--- a/data/trans_orig/P21D5_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P21D5_2023-Habitat-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, necesitándolo, no pudo recibir atención médica mental (psiquiatra) en 2023</t>
+          <t>Población que, necesitándolo, no pudo recibir atención médica mental (psiquiatra) en 2023 (tasa de respuesta: 99,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>241593</t>
+          <t>242663</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>258617</t>
+          <t>258814</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>90,62%</t>
+          <t>91,02%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>287549</t>
+          <t>287022</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>294981</t>
+          <t>295030</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>95,95%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>534180</t>
+          <t>532870</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>551133</t>
+          <t>550994</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,4%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5451</t>
+          <t>5392</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>20368</t>
+          <t>19505</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2970</t>
+          <t>2713</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10035</t>
+          <t>9746</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>9600</t>
+          <t>10011</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>25354</t>
+          <t>26022</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,6%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>715</t>
+          <t>738</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8329</t>
+          <t>10420</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4178</t>
+          <t>4193</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1460</t>
+          <t>1380</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>10154</t>
+          <t>10946</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,93%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3826</t>
+          <t>4086</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2870</t>
+          <t>2916</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4485</t>
+          <t>4562</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,81%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>151363</t>
+          <t>147111</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>634494</t>
+          <t>633557</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>22,34%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,23%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>413330</t>
+          <t>414073</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>429004</t>
+          <t>429293</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>396660</t>
+          <t>428916</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1054883</t>
+          <t>1054424</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>35,89%</t>
+          <t>38,81%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>95,41%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>22621</t>
+          <t>23476</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>508552</t>
+          <t>511768</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>77,24%</t>
+          <t>77,73%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12269</t>
+          <t>12183</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>26772</t>
+          <t>25710</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>42301</t>
+          <t>41562</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>706855</t>
+          <t>672366</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>63,96%</t>
+          <t>60,84%</t>
         </is>
       </c>
     </row>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4679</t>
+          <t>4759</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1617</t>
+          <t>1608</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8517</t>
+          <t>8148</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1924</t>
+          <t>1830</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>10146</t>
+          <t>9704</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,88%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2960</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>610</t>
+          <t>580</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6310</t>
+          <t>6015</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>401</t>
+          <t>522</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>6974</t>
+          <t>6303</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,57%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>296699</t>
+          <t>298883</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>320467</t>
+          <t>320494</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,73%</t>
+          <t>90,39%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>295959</t>
+          <t>295332</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>315519</t>
+          <t>314817</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,01%</t>
+          <t>89,81%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>604790</t>
+          <t>604003</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>632759</t>
+          <t>632961</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,7%</t>
+          <t>91,59%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>95,98%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7677</t>
+          <t>7646</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>33500</t>
+          <t>28634</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>9735</t>
+          <t>9594</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>24824</t>
+          <t>25294</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>19105</t>
+          <t>19689</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>44723</t>
+          <t>45378</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,88%</t>
         </is>
       </c>
     </row>
@@ -2099,7 +2099,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6561</t>
+          <t>6569</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1850</t>
+          <t>1903</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>16107</t>
+          <t>18874</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3062</t>
+          <t>3060</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>16669</t>
+          <t>16986</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,58%</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5331</t>
+          <t>4879</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2227,7 +2227,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,62 +2242,62 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>1004</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>1291</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>5024</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>0,15%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>0,39%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>1004</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>5064</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>0,15%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,76%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>373086</t>
+          <t>372842</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>392771</t>
+          <t>392140</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>91,45%</t>
+          <t>91,39%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>470370</t>
+          <t>470644</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>494469</t>
+          <t>495944</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>90,93%</t>
+          <t>90,98%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,87%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>849743</t>
+          <t>850365</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>882938</t>
+          <t>880876</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>91,84%</t>
+          <t>91,91%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>95,2%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>11010</t>
+          <t>11700</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>28065</t>
+          <t>29567</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>17675</t>
+          <t>17050</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>37925</t>
+          <t>38322</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>33488</t>
+          <t>35199</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>62073</t>
+          <t>61835</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,68%</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>779</t>
+          <t>759</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>10034</t>
+          <t>10178</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2683,7 +2683,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1609</t>
+          <t>1475</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>9029</t>
+          <t>8690</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>3396</t>
+          <t>3467</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>14778</t>
+          <t>15688</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2753,7 +2753,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,7%</t>
         </is>
       </c>
     </row>
@@ -2781,7 +2781,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5920</t>
+          <t>6076</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>915</t>
+          <t>1060</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>6870</t>
+          <t>6962</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>1919</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>10249</t>
+          <t>9956</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,08%</t>
         </is>
       </c>
     </row>
@@ -3006,12 +3006,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>816973</t>
+          <t>838681</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1581966</t>
+          <t>1584973</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3021,12 +3021,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>49,11%</t>
+          <t>50,41%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>95,27%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1486961</t>
+          <t>1486267</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1519843</t>
+          <t>1519465</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>93,4%</t>
+          <t>93,36%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3076,12 +3076,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>2174383</t>
+          <t>2184149</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>3085632</t>
+          <t>3086476</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>66,79%</t>
+          <t>67,09%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>94,78%</t>
+          <t>94,8%</t>
         </is>
       </c>
     </row>
@@ -3119,12 +3119,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>67168</t>
+          <t>65094</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>848528</t>
+          <t>817950</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>51,01%</t>
+          <t>49,17%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>53876</t>
+          <t>54084</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>82288</t>
+          <t>81291</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3189,12 +3189,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>133881</t>
+          <t>134421</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1054898</t>
+          <t>1045858</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>32,4%</t>
+          <t>32,12%</t>
         </is>
       </c>
     </row>
@@ -3232,12 +3232,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>4247</t>
+          <t>4055</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>17882</t>
+          <t>18380</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3247,12 +3247,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3267,12 +3267,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>9025</t>
+          <t>8293</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>23924</t>
+          <t>24159</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3302,12 +3302,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>15835</t>
+          <t>15669</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>38711</t>
+          <t>37149</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,14%</t>
         </is>
       </c>
     </row>
@@ -3345,12 +3345,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>789</t>
+          <t>698</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>8912</t>
+          <t>9228</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,04%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>2884</t>
+          <t>2979</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>11779</t>
+          <t>11657</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3395,12 +3395,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>4642</t>
+          <t>5164</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>15567</t>
+          <t>16093</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3430,12 +3430,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,49%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P21D5_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P21D5_2023-Habitat-trans_orig.xlsx
@@ -725,27 +725,27 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>252162</t>
+          <t>273235</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>242663</t>
+          <t>263596</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>258814</t>
+          <t>279722</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,83%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>91,02%</t>
+          <t>91,49%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>291836</t>
+          <t>315450</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>287022</t>
+          <t>310432</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>295030</t>
+          <t>319210</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>543997</t>
+          <t>588685</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>532870</t>
+          <t>577398</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>550994</t>
+          <t>596637</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>94,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,55%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>10629</t>
+          <t>11062</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5392</t>
+          <t>5290</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19505</t>
+          <t>20032</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5519</t>
+          <t>6138</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2713</t>
+          <t>2999</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9746</t>
+          <t>10958</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>16148</t>
+          <t>17200</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>10011</t>
+          <t>10390</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>26022</t>
+          <t>28809</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,71%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3115</t>
+          <t>3166</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>738</t>
+          <t>742</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10420</t>
+          <t>8543</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1196</t>
+          <t>1273</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -996,12 +996,12 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4193</t>
+          <t>4428</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>4311</t>
+          <t>4439</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1380</t>
+          <t>1780</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>10946</t>
+          <t>10071</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,65%</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>693</t>
+          <t>660</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1074,12 +1074,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4086</t>
+          <t>4367</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>578</t>
+          <t>648</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2916</t>
+          <t>3479</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1271</t>
+          <t>1308</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4562</t>
+          <t>4462</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,73%</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>266599</t>
+          <t>288123</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>266599</t>
+          <t>288123</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>266599</t>
+          <t>288123</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>299129</t>
+          <t>323509</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>299129</t>
+          <t>323509</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>299129</t>
+          <t>323509</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>565727</t>
+          <t>611632</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>565727</t>
+          <t>611632</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>565727</t>
+          <t>611632</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>394905</t>
+          <t>449776</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>147111</t>
+          <t>438067</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>633557</t>
+          <t>457404</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>59,98%</t>
+          <t>95,65%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>93,16%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>422170</t>
+          <t>475638</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>414073</t>
+          <t>465324</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>429293</t>
+          <t>483294</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>94,6%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>92,55%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>817075</t>
+          <t>925414</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>428916</t>
+          <t>909172</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1054424</t>
+          <t>937104</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>73,93%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>38,81%</t>
+          <t>93,44%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>96,31%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>262285</t>
+          <t>19169</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>23476</t>
+          <t>11606</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>511768</t>
+          <t>30857</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>39,84%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>77,73%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>18342</t>
+          <t>19990</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12183</t>
+          <t>13560</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>25710</t>
+          <t>29200</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>280627</t>
+          <t>39159</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>41562</t>
+          <t>28446</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>672366</t>
+          <t>55536</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>25,39%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>60,84%</t>
+          <t>5,71%</t>
         </is>
       </c>
     </row>
@@ -1520,7 +1520,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1199</t>
+          <t>1263</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1530,12 +1530,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4759</t>
+          <t>4553</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3943</t>
+          <t>4288</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1608</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8148</t>
+          <t>8698</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>5143</t>
+          <t>5551</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1830</t>
+          <t>2626</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>9704</t>
+          <t>10243</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>1,05%</t>
         </is>
       </c>
     </row>
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>580</t>
+          <t>696</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6015</t>
+          <t>7274</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>695</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>6303</t>
+          <t>7111</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,73%</t>
         </is>
       </c>
     </row>
@@ -1746,17 +1746,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>658389</t>
+          <t>470208</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>658389</t>
+          <t>470208</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>658389</t>
+          <t>470208</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>446772</t>
+          <t>502802</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>446772</t>
+          <t>502802</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>446772</t>
+          <t>502802</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1105162</t>
+          <t>973010</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1105162</t>
+          <t>973010</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1105162</t>
+          <t>973010</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>312815</t>
+          <t>356413</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>298883</t>
+          <t>344045</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>320494</t>
+          <t>365381</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>94,94%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,39%</t>
+          <t>91,64%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>308345</t>
+          <t>356600</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>295332</t>
+          <t>345705</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>314817</t>
+          <t>364462</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>94,33%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,81%</t>
+          <t>91,44%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>621160</t>
+          <t>713012</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>604003</t>
+          <t>697000</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>632961</t>
+          <t>724593</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>94,63%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,59%</t>
+          <t>92,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>96,17%</t>
         </is>
       </c>
     </row>
@@ -1976,32 +1976,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>14870</t>
+          <t>15938</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7646</t>
+          <t>7931</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>28634</t>
+          <t>29061</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2011,32 +2011,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>15160</t>
+          <t>16380</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>9594</t>
+          <t>10419</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>25294</t>
+          <t>26270</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>30030</t>
+          <t>32318</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>19689</t>
+          <t>21947</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>45378</t>
+          <t>48068</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,38%</t>
         </is>
       </c>
     </row>
@@ -2089,7 +2089,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1985</t>
+          <t>2082</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6569</t>
+          <t>6715</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>5319</t>
+          <t>5073</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1903</t>
+          <t>1438</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>18874</t>
+          <t>13497</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>7305</t>
+          <t>7155</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3060</t>
+          <t>3041</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>16986</t>
+          <t>16728</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,22%</t>
         </is>
       </c>
     </row>
@@ -2202,7 +2202,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1004</t>
+          <t>995</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -2212,12 +2212,12 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4879</t>
+          <t>5196</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -2227,7 +2227,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1004</t>
+          <t>995</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
@@ -2282,12 +2282,12 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5024</t>
+          <t>5910</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,78%</t>
         </is>
       </c>
     </row>
@@ -2315,17 +2315,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>330674</t>
+          <t>375428</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>330674</t>
+          <t>375428</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>330674</t>
+          <t>375428</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2350,17 +2350,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>328824</t>
+          <t>378053</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>328824</t>
+          <t>378053</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>328824</t>
+          <t>378053</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>659498</t>
+          <t>753480</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>659498</t>
+          <t>753480</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>659498</t>
+          <t>753480</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2432,32 +2432,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>383802</t>
+          <t>408392</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>372842</t>
+          <t>396788</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>392140</t>
+          <t>417622</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>94,24%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>91,39%</t>
+          <t>91,56%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,37%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,32 +2467,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>481583</t>
+          <t>450401</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>470644</t>
+          <t>439168</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>495944</t>
+          <t>458978</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>93,09%</t>
+          <t>91,92%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>90,98%</t>
+          <t>89,62%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>93,67%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>865385</t>
+          <t>858794</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>850365</t>
+          <t>843191</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>880876</t>
+          <t>872550</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>93,01%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>91,91%</t>
+          <t>91,32%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>94,5%</t>
         </is>
       </c>
     </row>
@@ -2545,32 +2545,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>19091</t>
+          <t>19575</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>11700</t>
+          <t>11746</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>29567</t>
+          <t>30733</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,32 +2580,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>28477</t>
+          <t>31948</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>17050</t>
+          <t>24922</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>38322</t>
+          <t>42364</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>47568</t>
+          <t>51523</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>35199</t>
+          <t>40157</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>61835</t>
+          <t>66012</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>7,15%</t>
         </is>
       </c>
     </row>
@@ -2658,32 +2658,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3376</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>759</t>
+          <t>729</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>10178</t>
+          <t>11876</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2693,32 +2693,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>4206</t>
+          <t>4516</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1475</t>
+          <t>1655</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>8690</t>
+          <t>9488</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>7582</t>
+          <t>8177</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>3467</t>
+          <t>3570</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>15688</t>
+          <t>16394</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,78%</t>
         </is>
       </c>
     </row>
@@ -2771,7 +2771,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>1684</t>
+          <t>1731</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -2781,12 +2781,12 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6076</t>
+          <t>5864</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>3043</t>
+          <t>3145</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1060</t>
+          <t>1206</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>6962</t>
+          <t>7732</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>4727</t>
+          <t>4876</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1919</t>
+          <t>2137</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>9956</t>
+          <t>10739</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,16%</t>
         </is>
       </c>
     </row>
@@ -2884,17 +2884,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>407953</t>
+          <t>433359</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>407953</t>
+          <t>433359</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>407953</t>
+          <t>433359</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>517309</t>
+          <t>490010</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>517309</t>
+          <t>490010</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>517309</t>
+          <t>490010</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>925261</t>
+          <t>923370</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>925261</t>
+          <t>923370</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>925261</t>
+          <t>923370</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3001,32 +3001,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1343683</t>
+          <t>1487816</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>838681</t>
+          <t>1464914</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1584973</t>
+          <t>1505429</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>80,77%</t>
+          <t>94,94%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>50,41%</t>
+          <t>93,48%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3036,32 +3036,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1503933</t>
+          <t>1598089</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1486267</t>
+          <t>1580219</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1519465</t>
+          <t>1613685</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>94,32%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>93,26%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3071,32 +3071,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>2847617</t>
+          <t>3085905</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>2184149</t>
+          <t>3059035</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>3086476</t>
+          <t>3108915</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>87,47%</t>
+          <t>94,62%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>67,09%</t>
+          <t>93,79%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>95,32%</t>
         </is>
       </c>
     </row>
@@ -3114,32 +3114,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>306874</t>
+          <t>65745</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>65094</t>
+          <t>49074</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>817950</t>
+          <t>88048</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>49,17%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3149,32 +3149,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>67498</t>
+          <t>74456</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>54084</t>
+          <t>61539</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>81291</t>
+          <t>89425</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,32 +3184,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>374372</t>
+          <t>140201</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>134421</t>
+          <t>119216</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1045858</t>
+          <t>167189</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>32,12%</t>
+          <t>5,13%</t>
         </is>
       </c>
     </row>
@@ -3227,32 +3227,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>9676</t>
+          <t>10173</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>4055</t>
+          <t>4872</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>18380</t>
+          <t>19079</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3262,67 +3262,67 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>14665</t>
+          <t>15150</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>8293</t>
+          <t>9186</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>24159</t>
+          <t>24995</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
+          <t>0,54%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>1,48%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>25322</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>16975</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>36487</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>0,78%</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
           <t>0,52%</t>
         </is>
       </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>1,52%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>24340</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>15669</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>37149</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>0,75%</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>0,48%</t>
-        </is>
-      </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,12%</t>
         </is>
       </c>
     </row>
@@ -3340,67 +3340,67 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3381</t>
+          <t>3385</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>698</t>
+          <t>989</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>9228</t>
+          <t>8574</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
+          <t>0,22%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>0,06%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>0,55%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>6679</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>3369</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>12548</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>0,39%</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
           <t>0,2%</t>
         </is>
       </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>0,04%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>0,55%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>5938</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>2979</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>11657</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
-      <c r="O27" s="2" t="inlineStr">
-        <is>
-          <t>0,19%</t>
-        </is>
-      </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3410,32 +3410,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>9319</t>
+          <t>10064</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>5164</t>
+          <t>5702</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>16093</t>
+          <t>16740</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,51%</t>
         </is>
       </c>
     </row>
@@ -3453,17 +3453,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>1663614</t>
+          <t>1567118</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1663614</t>
+          <t>1567118</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1663614</t>
+          <t>1567118</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>1592034</t>
+          <t>1694374</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1592034</t>
+          <t>1694374</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1592034</t>
+          <t>1694374</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>3255648</t>
+          <t>3261492</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3255648</t>
+          <t>3261492</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3255648</t>
+          <t>3261492</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
